--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487083_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487083_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.517</v>
+        <v>5.8862</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0746</v>
+        <v>5.9352</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5576</v>
+        <v>-0.049</v>
       </c>
       <c r="G2" t="n">
         <v>4.3425</v>
@@ -610,13 +610,13 @@
         <v>1.5441</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8652</v>
+        <v>0.504</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8791</v>
+        <v>-0.0185</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0139</v>
+        <v>0.5225</v>
       </c>
       <c r="V2" t="n">
         <v>3.3558</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.006</v>
+        <v>3.7224</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2173</v>
+        <v>3.9778</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7887</v>
+        <v>-0.2553</v>
       </c>
       <c r="G3" t="n">
         <v>1.6438</v>
@@ -688,13 +688,13 @@
         <v>1.9301</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4165</v>
+        <v>1.1329</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.805</v>
+        <v>-0.0446</v>
       </c>
       <c r="U3" t="n">
-        <v>2.2215</v>
+        <v>1.1775</v>
       </c>
       <c r="V3" t="n">
         <v>-0.9843</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. VASQUEZ BAUTISTA</t>
+          <t>J. TEJERINA TEJEDO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6259</v>
+        <v>3.3451</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8761</v>
+        <v>3.3432</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7498</v>
+        <v>0.0019</v>
       </c>
       <c r="G4" t="n">
-        <v>3.8333</v>
+        <v>5.6487</v>
       </c>
       <c r="H4" t="n">
-        <v>2.2603</v>
+        <v>1.211</v>
       </c>
       <c r="I4" t="n">
-        <v>1.573</v>
+        <v>4.4376</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2311</v>
+        <v>4.2266</v>
       </c>
       <c r="K4" t="n">
-        <v>1.9869</v>
+        <v>1.1178</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2442</v>
+        <v>3.1089</v>
       </c>
       <c r="M4" t="n">
-        <v>1.6022</v>
+        <v>1.422</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2734</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="O4" t="n">
         <v>1.3288</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.3161</v>
+        <v>-0.772</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.8602</v>
+        <v>-1.9301</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5441</v>
+        <v>1.158</v>
       </c>
       <c r="S4" t="n">
-        <v>3.3367</v>
+        <v>0.9244</v>
       </c>
       <c r="T4" t="n">
-        <v>2.5052</v>
+        <v>0.4326</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8315</v>
+        <v>0.4918</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.228</v>
+        <v>-2.4559</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.614</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.228</v>
+        <v>-3.0699</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. TEJERINA TEJEDO</t>
+          <t>A. VASQUEZ BAUTISTA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7234</v>
+        <v>2.2636</v>
       </c>
       <c r="E5" t="n">
-        <v>3.0427</v>
+        <v>-0.3256</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3193</v>
+        <v>2.5891</v>
       </c>
       <c r="G5" t="n">
-        <v>5.6487</v>
+        <v>3.8333</v>
       </c>
       <c r="H5" t="n">
-        <v>1.211</v>
+        <v>2.2603</v>
       </c>
       <c r="I5" t="n">
-        <v>4.4376</v>
+        <v>1.573</v>
       </c>
       <c r="J5" t="n">
-        <v>4.2266</v>
+        <v>2.2311</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1178</v>
+        <v>1.9869</v>
       </c>
       <c r="L5" t="n">
-        <v>3.1089</v>
+        <v>0.2442</v>
       </c>
       <c r="M5" t="n">
-        <v>1.422</v>
+        <v>1.6022</v>
       </c>
       <c r="N5" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.2734</v>
       </c>
       <c r="O5" t="n">
         <v>1.3288</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.772</v>
+        <v>-2.3161</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9301</v>
+        <v>-3.8602</v>
       </c>
       <c r="R5" t="n">
-        <v>1.158</v>
+        <v>1.5441</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3027</v>
+        <v>1.9744</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1322</v>
+        <v>1.3035</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1705</v>
+        <v>0.6709000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.4559</v>
+        <v>-1.228</v>
       </c>
       <c r="W5" t="n">
-        <v>0.614</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.0699</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.6801</v>
+        <v>1.7718</v>
       </c>
       <c r="E6" t="n">
-        <v>2.258</v>
+        <v>1.4569</v>
       </c>
       <c r="F6" t="n">
-        <v>0.422</v>
+        <v>0.3149</v>
       </c>
       <c r="G6" t="n">
         <v>2.0432</v>
@@ -922,13 +922,13 @@
         <v>0.965</v>
       </c>
       <c r="S6" t="n">
-        <v>1.8878</v>
+        <v>0.9796</v>
       </c>
       <c r="T6" t="n">
-        <v>1.1105</v>
+        <v>0.3094</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7773</v>
+        <v>0.6702</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2859</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6065</v>
+        <v>0.4261</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7235</v>
+        <v>0.6234</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.117</v>
+        <v>-0.1973</v>
       </c>
       <c r="G7" t="n">
         <v>-0.2455</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.852</v>
+        <v>0.6716</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6821</v>
+        <v>0.582</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1699</v>
+        <v>0.0896</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2321</v>
+        <v>0.1786</v>
       </c>
       <c r="E8" t="n">
         <v>-0.0162</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2483</v>
+        <v>0.1948</v>
       </c>
       <c r="G8" t="n">
         <v>0.3564</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1243</v>
+        <v>-0.1778</v>
       </c>
       <c r="T8" t="n">
         <v>-0.119</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0053</v>
+        <v>-0.0588</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2057</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0766</v>
+        <v>0.377</v>
       </c>
       <c r="F9" t="n">
         <v>-0.2823</v>
@@ -1156,10 +1156,10 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0595</v>
+        <v>0.2409</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2234</v>
+        <v>0.077</v>
       </c>
       <c r="U9" t="n">
         <v>0.1639</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.156</v>
+        <v>-1.3771</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5516</v>
+        <v>-0.6924</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6045</v>
+        <v>-0.6848</v>
       </c>
       <c r="G10" t="n">
         <v>-0.9981</v>
@@ -1234,13 +1234,13 @@
         <v>0.193</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6141</v>
+        <v>0.393</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3107</v>
+        <v>0.1699</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3034</v>
+        <v>0.2231</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.697</v>
+        <v>-1.5687</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7341</v>
+        <v>-0.8735000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9628</v>
+        <v>-0.6951000000000001</v>
       </c>
       <c r="G11" t="n">
         <v>-3.1428</v>
@@ -1312,13 +1312,13 @@
         <v>1.5441</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4614</v>
+        <v>0.6669</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3886</v>
+        <v>0.472</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0727</v>
+        <v>0.195</v>
       </c>
       <c r="V11" t="n">
         <v>0.3281</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.7723</v>
+        <v>-4.159</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.34</v>
+        <v>-2.9408</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4323</v>
+        <v>-1.2182</v>
       </c>
       <c r="G12" t="n">
         <v>-4.429</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.9426</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8739</v>
+        <v>0.273</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0687</v>
+        <v>0.2829</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2859</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.7684</v>
+        <v>-4.4948</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.2542</v>
+        <v>-3.1947</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.5142</v>
+        <v>-1.3001</v>
       </c>
       <c r="G13" t="n">
         <v>-3.0738</v>
@@ -1468,13 +1468,13 @@
         <v>0.772</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2736</v>
+        <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4032</v>
+        <v>-0.3437</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1295</v>
+        <v>0.3437</v>
       </c>
       <c r="V13" t="n">
         <v>-1.228</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.791600000000001</v>
+        <v>6.088900000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>7.372699999999999</v>
+        <v>7.670300000000002</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.5812</v>
+        <v>-1.5814</v>
       </c>
       <c r="G14" t="n">
         <v>5.504399999999999</v>
@@ -1546,13 +1546,13 @@
         <v>9.650399999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>7.5684</v>
+        <v>7.8658</v>
       </c>
       <c r="T14" t="n">
-        <v>2.7963</v>
+        <v>3.0936</v>
       </c>
       <c r="U14" t="n">
-        <v>4.7721</v>
+        <v>4.7723</v>
       </c>
       <c r="V14" t="n">
         <v>-2.456</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>O. HERNANDEZ HERNANDEZ</t>
+          <t>J. OTERO GONZALEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2644</v>
+        <v>3.0751</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1628</v>
+        <v>4.8347</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1016</v>
+        <v>-1.7595</v>
       </c>
       <c r="G15" t="n">
-        <v>1.276</v>
+        <v>1.1006</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6456</v>
+        <v>0.353</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6304999999999999</v>
+        <v>0.7476</v>
       </c>
       <c r="J15" t="n">
-        <v>1.9898</v>
+        <v>3.236</v>
       </c>
       <c r="K15" t="n">
-        <v>1.8677</v>
+        <v>2.5769</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1221</v>
+        <v>0.6591</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7138</v>
+        <v>-2.1354</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.2222</v>
+        <v>-2.2239</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5084</v>
+        <v>0.0885</v>
       </c>
       <c r="P15" t="n">
-        <v>0.386</v>
+        <v>1.9301</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.965</v>
+        <v>-0.193</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3511</v>
+        <v>2.1231</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8303</v>
+        <v>-0.8976</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8521</v>
+        <v>-0.6642</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9782</v>
+        <v>-0.2334</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.228</v>
+        <v>0.9421</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2859</v>
+        <v>2.4559</v>
       </c>
       <c r="X15" t="n">
         <v>-1.5138</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. OTERO GONZALEZ</t>
+          <t>O. HERNANDEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.6878</v>
+        <v>1.1734</v>
       </c>
       <c r="E16" t="n">
-        <v>4.6344</v>
+        <v>1.6607</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.9466</v>
+        <v>-0.4873</v>
       </c>
       <c r="G16" t="n">
-        <v>1.1006</v>
+        <v>1.276</v>
       </c>
       <c r="H16" t="n">
-        <v>0.353</v>
+        <v>0.6456</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7476</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>3.236</v>
+        <v>1.9898</v>
       </c>
       <c r="K16" t="n">
-        <v>2.5769</v>
+        <v>1.8677</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6591</v>
+        <v>0.1221</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.1354</v>
+        <v>-0.7138</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.2239</v>
+        <v>-1.2222</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0885</v>
+        <v>0.5084</v>
       </c>
       <c r="P16" t="n">
-        <v>1.9301</v>
+        <v>0.386</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.193</v>
+        <v>-0.965</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1231</v>
+        <v>1.3511</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.285</v>
+        <v>0.7393</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8645</v>
+        <v>0.35</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4204</v>
+        <v>0.3893</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9421</v>
+        <v>-1.228</v>
       </c>
       <c r="W16" t="n">
-        <v>2.4559</v>
+        <v>0.2859</v>
       </c>
       <c r="X16" t="n">
         <v>-1.5138</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N. NDOYE</t>
+          <t>E. CARPINTERO REVILLA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0048</v>
+        <v>0.7951</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5659</v>
+        <v>1.6968</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5611</v>
+        <v>-0.9016999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.5461</v>
+        <v>0.1209</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.981</v>
+        <v>-1.6084</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4348</v>
+        <v>1.7293</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.2324</v>
+        <v>1.8225</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.2731</v>
+        <v>0.4552</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0407</v>
+        <v>1.3674</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3137</v>
+        <v>-1.7016</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7079</v>
+        <v>-2.0636</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3941</v>
+        <v>0.362</v>
       </c>
       <c r="P17" t="n">
-        <v>1.158</v>
+        <v>1.3511</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.193</v>
+        <v>-0.965</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3511</v>
+        <v>2.3161</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2307</v>
+        <v>-1.5768</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6544</v>
+        <v>-0.6745</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4237</v>
+        <v>-0.9023</v>
       </c>
       <c r="V17" t="n">
-        <v>0.614</v>
+        <v>0.8999</v>
       </c>
       <c r="W17" t="n">
         <v>1.5138</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.8999</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. CARPINTERO REVILLA</t>
+          <t>N. NDOYE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1069</v>
+        <v>-0.3528</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1961</v>
+        <v>-0.5659</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.303</v>
+        <v>0.2131</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1209</v>
+        <v>-1.5461</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.6084</v>
+        <v>-1.981</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7293</v>
+        <v>0.4348</v>
       </c>
       <c r="J18" t="n">
-        <v>1.8225</v>
+        <v>-1.2324</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4552</v>
+        <v>-1.2731</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3674</v>
+        <v>0.0407</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.7016</v>
+        <v>-0.3137</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.0636</v>
+        <v>-0.7079</v>
       </c>
       <c r="O18" t="n">
-        <v>0.362</v>
+        <v>0.3941</v>
       </c>
       <c r="P18" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-0.193</v>
+      </c>
+      <c r="R18" t="n">
         <v>1.3511</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-0.965</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.3161</v>
-      </c>
       <c r="S18" t="n">
-        <v>-2.4787</v>
+        <v>-0.5787</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1752</v>
+        <v>-0.6544</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.3035</v>
+        <v>0.0757</v>
       </c>
       <c r="V18" t="n">
-        <v>0.8999</v>
+        <v>0.614</v>
       </c>
       <c r="W18" t="n">
         <v>1.5138</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.614</v>
+        <v>-0.8999</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6526</v>
+        <v>-0.3644</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5641</v>
+        <v>0.2637</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2167</v>
+        <v>-0.6281</v>
       </c>
       <c r="G19" t="n">
         <v>1.0161</v>
@@ -1936,13 +1936,13 @@
         <v>2.3161</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3755</v>
+        <v>-1.0873</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1969</v>
+        <v>-0.4973</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.1786</v>
+        <v>-0.59</v>
       </c>
       <c r="V19" t="n">
         <v>0.2859</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.47</v>
+        <v>-0.6947</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8948</v>
+        <v>-0.4943</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5752</v>
+        <v>-0.2004</v>
       </c>
       <c r="G20" t="n">
         <v>-4.0353</v>
@@ -2014,13 +2014,13 @@
         <v>1.5441</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.1416</v>
+        <v>-1.3663</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1898</v>
+        <v>-0.7892</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9518</v>
+        <v>-0.5770999999999999</v>
       </c>
       <c r="V20" t="n">
         <v>3.3558</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3253</v>
+        <v>-2.0183</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6061</v>
+        <v>-1.4058</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7192</v>
+        <v>-0.6124000000000001</v>
       </c>
       <c r="G21" t="n">
         <v>0.5532</v>
@@ -2092,13 +2092,13 @@
         <v>0.386</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8784999999999999</v>
+        <v>-0.5714</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6544</v>
+        <v>-0.4541</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2241</v>
+        <v>-0.1173</v>
       </c>
       <c r="V21" t="n">
         <v>-1.228</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0486</v>
+        <v>-2.6752</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5734</v>
+        <v>-1.1729</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4752</v>
+        <v>-1.5023</v>
       </c>
       <c r="G22" t="n">
         <v>-0.9574</v>
@@ -2170,13 +2170,13 @@
         <v>1.9301</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6353</v>
+        <v>-1.2618</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.5467</v>
+        <v>-1.1461</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0886</v>
+        <v>-0.1157</v>
       </c>
       <c r="V22" t="n">
         <v>-1.228</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.1356</v>
+        <v>-4.0622</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3357</v>
+        <v>-3.2356</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7999000000000001</v>
+        <v>-0.8267</v>
       </c>
       <c r="G23" t="n">
         <v>-3.0323</v>
@@ -2248,13 +2248,13 @@
         <v>1.158</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3735</v>
+        <v>-0.3001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3424</v>
+        <v>-0.2422</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0311</v>
+        <v>-0.0579</v>
       </c>
       <c r="V23" t="n">
         <v>0.0422</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.791599999999999</v>
+        <v>-5.124</v>
       </c>
       <c r="E24" t="n">
-        <v>1.5815</v>
+        <v>1.5814</v>
       </c>
       <c r="F24" t="n">
-        <v>-7.3731</v>
+        <v>-6.705299999999999</v>
       </c>
       <c r="G24" t="n">
         <v>-5.504300000000001</v>
@@ -2326,13 +2326,13 @@
         <v>14.4757</v>
       </c>
       <c r="S24" t="n">
-        <v>-7.5685</v>
+        <v>-6.9007</v>
       </c>
       <c r="T24" t="n">
-        <v>-4.7722</v>
+        <v>-4.772</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.7962</v>
+        <v>-2.1287</v>
       </c>
       <c r="V24" t="n">
         <v>2.4559</v>
